--- a/data/trans_orig/IP07A12-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A12-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35666</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22989</t>
+          <t>23035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>40628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17094</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23562</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38453</t>
+          <t>38293</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41973</t>
+          <t>41983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62390</t>
+          <t>62170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57013</t>
+          <t>57243</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79075</t>
+          <t>79285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104895</t>
+          <t>104555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134999</t>
+          <t>134085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79286</t>
+          <t>79681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>102114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94270</t>
+          <t>93971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117363</t>
+          <t>118386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178315</t>
+          <t>177702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212467</t>
+          <t>213211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>59867</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>41164</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>61019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>86994</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114740</t>
+          <t>115522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29436</t>
+          <t>28966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>38705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56233</t>
+          <t>56306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31480</t>
+          <t>31757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59697</t>
+          <t>59203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>20463</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>35886</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78698</t>
+          <t>78941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105359</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89171</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116899</t>
+          <t>117555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174352</t>
+          <t>175950</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212231</t>
+          <t>213962</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115935</t>
+          <t>118648</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>145714</t>
+          <t>146218</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129971</t>
+          <t>130097</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>159913</t>
+          <t>160744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>259068</t>
+          <t>256655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>299854</t>
+          <t>297735</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>67925</t>
+          <t>68341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92720</t>
+          <t>91515</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91418</t>
+          <t>92220</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>142519</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>175830</t>
+          <t>176008</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>14897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26413</t>
+          <t>27203</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27359</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>22221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>37422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18251</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20706</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35196</t>
+          <t>35132</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65329</t>
+          <t>63916</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87632</t>
+          <t>86507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78351</t>
+          <t>78175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103549</t>
+          <t>102034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149726</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182246</t>
+          <t>185427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>70444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92669</t>
+          <t>93647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68392</t>
+          <t>69262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92316</t>
+          <t>92899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144133</t>
+          <t>144899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177011</t>
+          <t>179380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30908</t>
+          <t>31618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50180</t>
+          <t>50308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>31080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50332</t>
+          <t>49297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>66048</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93258</t>
+          <t>93794</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>27167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>30310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43468</t>
+          <t>43474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>36679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57522</t>
+          <t>57157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75897</t>
+          <t>76135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>23601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>10579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24587</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22495</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117966</t>
+          <t>117786</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147421</t>
+          <t>148566</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120179</t>
+          <t>118325</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148416</t>
+          <t>148672</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>243996</t>
+          <t>247239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>288369</t>
+          <t>289003</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100243</t>
+          <t>100312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128659</t>
+          <t>128688</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>98118</t>
+          <t>95873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124521</t>
+          <t>126267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>204397</t>
+          <t>203819</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>244001</t>
+          <t>244778</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49612</t>
+          <t>50081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>73224</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>72845</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>106404</t>
+          <t>106535</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>139201</t>
+          <t>139621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>20386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>38287</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>19818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>18615</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26304</t>
+          <t>26177</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20609</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60710</t>
+          <t>61536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83682</t>
+          <t>85576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79160</t>
+          <t>79744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105287</t>
+          <t>105542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147932</t>
+          <t>146494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183952</t>
+          <t>183417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62199</t>
+          <t>63405</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85821</t>
+          <t>86091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61038</t>
+          <t>60740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85102</t>
+          <t>85314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130623</t>
+          <t>129277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165001</t>
+          <t>163133</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>63577</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87136</t>
+          <t>86822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56974</t>
+          <t>57113</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80742</t>
+          <t>79829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>127260</t>
+          <t>127569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>161749</t>
+          <t>160876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26982</t>
+          <t>27106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>39491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33406</t>
+          <t>33671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24719</t>
+          <t>24992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48124</t>
+          <t>48432</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67994</t>
+          <t>69359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>18649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31394</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46619</t>
+          <t>46374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65850</t>
+          <t>66075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35843</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91048</t>
+          <t>90749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120282</t>
+          <t>119868</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113995</t>
+          <t>114917</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144474</t>
+          <t>143358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214699</t>
+          <t>213002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255990</t>
+          <t>256550</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99833</t>
+          <t>99531</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>129450</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96433</t>
+          <t>96850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>125192</t>
+          <t>125083</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>203631</t>
+          <t>202881</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243925</t>
+          <t>244189</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80941</t>
+          <t>80969</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>109704</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>82938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109480</t>
+          <t>112121</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>169896</t>
+          <t>170777</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>209574</t>
+          <t>209320</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39387</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>29855</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63935</t>
+          <t>65543</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
